--- a/LISTAS/ma/SOGA MULTIFILAMENTO.xlsx
+++ b/LISTAS/ma/SOGA MULTIFILAMENTO.xlsx
@@ -761,14 +761,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45163.60917233465</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+        <v>45253</v>
+      </c>
+    </row>
     <row r="7" ht="22.5" customHeight="1" s="18">
       <c r="A7" s="20" t="inlineStr">
         <is>
@@ -850,7 +845,7 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>18.875</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="18">
@@ -870,7 +865,7 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>21.5</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="18">
@@ -890,7 +885,7 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>26</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="18">
@@ -910,7 +905,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>33.125</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" s="18">
@@ -930,7 +925,7 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>66.25</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" s="18">
@@ -950,7 +945,7 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>99.125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" s="18">
@@ -970,7 +965,7 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>155</v>
+        <v>168.3</v>
       </c>
     </row>
     <row r="21" ht="23.25" customHeight="1" s="18" thickBot="1">
@@ -990,29 +985,12 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>213.75</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1" s="18">
       <c r="G22" s="16" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>

--- a/LISTAS/ma/SOGA MULTIFILAMENTO.xlsx
+++ b/LISTAS/ma/SOGA MULTIFILAMENTO.xlsx
@@ -761,7 +761,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="18">

--- a/LISTAS/ma/SOGA MULTIFILAMENTO.xlsx
+++ b/LISTAS/ma/SOGA MULTIFILAMENTO.xlsx
@@ -761,7 +761,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="18">

--- a/LISTAS/ma/SOGA MULTIFILAMENTO.xlsx
+++ b/LISTAS/ma/SOGA MULTIFILAMENTO.xlsx
@@ -761,9 +761,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45266</v>
-      </c>
-    </row>
+        <v>45258.54560011531</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7" ht="22.5" customHeight="1" s="18">
       <c r="A7" s="20" t="inlineStr">
         <is>
@@ -845,7 +850,7 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>20.3</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="18">
@@ -865,7 +870,7 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>23.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="18">
@@ -885,7 +890,7 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>28.01</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="18">
@@ -905,7 +910,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>35.7</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" s="18">
@@ -925,7 +930,7 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>71.3</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" s="18">
@@ -945,7 +950,7 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>107</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" s="18">
@@ -965,7 +970,7 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>168.3</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" ht="23.25" customHeight="1" s="18" thickBot="1">
@@ -985,12 +990,29 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>233</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1" s="18">
       <c r="G22" s="16" t="n"/>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>

--- a/LISTAS/ma/SOGA MULTIFILAMENTO.xlsx
+++ b/LISTAS/ma/SOGA MULTIFILAMENTO.xlsx
@@ -761,14 +761,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45258.54560011531</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+        <v>45286</v>
+      </c>
+    </row>
     <row r="7" ht="22.5" customHeight="1" s="18">
       <c r="A7" s="20" t="inlineStr">
         <is>
@@ -850,7 +845,7 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>29.4</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="18">
@@ -870,7 +865,7 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>33.5</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="18">
@@ -890,7 +885,7 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>40.5</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="18">
@@ -910,7 +905,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>51.5</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" s="18">
@@ -930,7 +925,7 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>103</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" s="18">
@@ -950,7 +945,7 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>155</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" s="18">
@@ -970,7 +965,7 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>242</v>
+        <v>168.3</v>
       </c>
     </row>
     <row r="21" ht="23.25" customHeight="1" s="18" thickBot="1">
@@ -990,29 +985,12 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>333</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1" s="18">
       <c r="G22" s="16" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
